--- a/Gráfico_Grupo de Despesa.xlsx
+++ b/Gráfico_Grupo de Despesa.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Rei-1cpd003\coord_plan_institucional\DADOS CPI\Orçamento\2026\EXECUÇÃO ORÇAMENTÁRIA\RELEXORC_CSV\Saida_PowerBI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF1A691-A861-49A7-801A-16BC5FC054B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C78E0AF-2888-44E8-9688-1C9EF72027F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{BD803231-520B-43E5-B415-970328918330}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BD803231-520B-43E5-B415-970328918330}"/>
   </bookViews>
   <sheets>
-    <sheet name="Exec_Por Grupo" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
-    <sheet name="Receita X Despesa" sheetId="3" r:id="rId3"/>
+    <sheet name="Receita X Despesa" sheetId="3" r:id="rId1"/>
+    <sheet name="Exec_Por Grupo" sheetId="1" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Planilha1!$A$1:$P$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Planilha1!$A$1:$P$59</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2700,6 +2700,554 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20333736-63C4-4805-88B4-CD691F856C39}">
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="27">
+        <v>46023</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1">
+        <v>84416666.666666672</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="27">
+        <v>46023</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1">
+        <v>62844099.030000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="27">
+        <v>46023</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1">
+        <v>154635427.19999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="27">
+        <v>46023</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1">
+        <f>C3-C4</f>
+        <v>-91791328.169999987</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="27">
+        <v>46054</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1">
+        <v>84416666.666666672</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>46054</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1">
+        <v>71107409.859999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="27">
+        <v>46054</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>65867006.619999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <v>46054</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1">
+        <f>C7-C8</f>
+        <v>5240403.2400000021</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <v>46082</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1">
+        <v>84416666.666666672</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <v>46082</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1">
+        <v>75044984.989999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="27">
+        <v>46082</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1">
+        <v>54581181.280000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>46082</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <f>C11-C12</f>
+        <v>20463803.709999993</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <v>46113</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="1">
+        <v>84416666.666666672</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <v>46113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="1">
+        <v>91828183.739999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <v>46113</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="1">
+        <v>41371067.399999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <v>46113</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="1">
+        <f>C15-C16</f>
+        <v>50457116.339999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <v>46143</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="1">
+        <v>84416666.666666672</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>46143</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="1">
+        <v>77415932.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <v>46143</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="1">
+        <v>80184171.170000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <v>46143</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="1">
+        <f>C19-C20</f>
+        <v>-2768238.6700000018</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <v>46174</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="1">
+        <v>84416666.666666672</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <v>46174</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="1">
+        <v>75166762.640000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <v>46174</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="1">
+        <v>92382151.069999993</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <v>46174</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="1">
+        <f>C23-C24</f>
+        <v>-17215388.429999992</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <v>46204</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="1">
+        <v>84416666.666666672</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <v>46204</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="1">
+        <v>70888043.189999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <v>46204</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="1">
+        <v>99462564.390000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <v>46204</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="1">
+        <f>C27-C28</f>
+        <v>-28574521.200000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <v>46235</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="1">
+        <v>84416666.666666672</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <v>46235</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <v>46235</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="1"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <v>46235</v>
+      </c>
+      <c r="B33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="1">
+        <f>C31-C32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <v>46266</v>
+      </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="1">
+        <v>84416666.666666672</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <v>46266</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="1"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <v>46266</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="1"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="27">
+        <v>46266</v>
+      </c>
+      <c r="B37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="1">
+        <f>C35-C36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <v>46296</v>
+      </c>
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="1">
+        <v>84416666.666666672</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <v>46296</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="1"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="27">
+        <v>46296</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="1"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="27">
+        <v>46296</v>
+      </c>
+      <c r="B41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="1">
+        <f>C39-C40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <v>46327</v>
+      </c>
+      <c r="B42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="1">
+        <v>84416666.666666672</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="27">
+        <v>46327</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="1"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <v>46327</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="1"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <v>46327</v>
+      </c>
+      <c r="B45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" s="1">
+        <f>C43-C44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <v>46357</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="1">
+        <v>84416666.666666672</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="27">
+        <v>46357</v>
+      </c>
+      <c r="B47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="1"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <v>46357</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="1"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <v>46357</v>
+      </c>
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" s="1">
+        <f>C47-C48</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F53F72-D795-49FC-9398-FBDE53A0A7F9}">
   <dimension ref="B3:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2827,7 +3375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAC02C4-A2C3-4869-A45C-FC4CAB74D8EC}">
   <dimension ref="A2:U59"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -4066,552 +4614,4 @@
   <pageSetup paperSize="9" scale="24" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20333736-63C4-4805-88B4-CD691F856C39}">
-  <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" hidden="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="27">
-        <v>46023</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="1">
-        <v>84416666.666666672</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="27">
-        <v>46023</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="1">
-        <v>62844099.030000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="27">
-        <v>46023</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1">
-        <v>154635427.19999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="27">
-        <v>46023</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1">
-        <f>C3-C4</f>
-        <v>-91791328.169999987</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="27">
-        <v>46054</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1">
-        <v>84416666.666666672</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
-        <v>46054</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="1">
-        <v>71107409.859999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="27">
-        <v>46054</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="1">
-        <v>65867006.619999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
-        <v>46054</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1">
-        <f>C7-C8</f>
-        <v>5240403.2400000021</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="27">
-        <v>46082</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1">
-        <v>84416666.666666672</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="27">
-        <v>46082</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="1">
-        <v>75044984.989999995</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="27">
-        <v>46082</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="1">
-        <v>54581181.280000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="27">
-        <v>46082</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="1">
-        <f>C11-C12</f>
-        <v>20463803.709999993</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="27">
-        <v>46113</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="1">
-        <v>84416666.666666672</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="27">
-        <v>46113</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="1">
-        <v>91828183.739999995</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="27">
-        <v>46113</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="1">
-        <v>41371067.399999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="27">
-        <v>46113</v>
-      </c>
-      <c r="B17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="1">
-        <f>C15-C16</f>
-        <v>50457116.339999996</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="27">
-        <v>46143</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="1">
-        <v>84416666.666666672</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="27">
-        <v>46143</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="1">
-        <v>77415932.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="27">
-        <v>46143</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="1">
-        <v>80184171.170000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="27">
-        <v>46143</v>
-      </c>
-      <c r="B21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="1">
-        <f>C19-C20</f>
-        <v>-2768238.6700000018</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="27">
-        <v>46174</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="1">
-        <v>84416666.666666672</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="27">
-        <v>46174</v>
-      </c>
-      <c r="B23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="1">
-        <v>75166762.640000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="27">
-        <v>46174</v>
-      </c>
-      <c r="B24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="1">
-        <v>92382151.069999993</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
-        <v>46174</v>
-      </c>
-      <c r="B25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="1">
-        <f>C23-C24</f>
-        <v>-17215388.429999992</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="27">
-        <v>46204</v>
-      </c>
-      <c r="B26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="1">
-        <v>84416666.666666672</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="27">
-        <v>46204</v>
-      </c>
-      <c r="B27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="1">
-        <v>70888043.189999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="27">
-        <v>46204</v>
-      </c>
-      <c r="B28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="1">
-        <v>99462564.390000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="27">
-        <v>46204</v>
-      </c>
-      <c r="B29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="1">
-        <f>C27-C28</f>
-        <v>-28574521.200000003</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="27">
-        <v>46235</v>
-      </c>
-      <c r="B30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="1">
-        <v>84416666.666666672</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="27">
-        <v>46235</v>
-      </c>
-      <c r="B31" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="27">
-        <v>46235</v>
-      </c>
-      <c r="B32" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="27">
-        <v>46235</v>
-      </c>
-      <c r="B33" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="1">
-        <f>C31-C32</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="27">
-        <v>46266</v>
-      </c>
-      <c r="B34" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="1">
-        <v>84416666.666666672</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="27">
-        <v>46266</v>
-      </c>
-      <c r="B35" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="27">
-        <v>46266</v>
-      </c>
-      <c r="B36" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="1"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="27">
-        <v>46266</v>
-      </c>
-      <c r="B37" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="1">
-        <f>C35-C36</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="27">
-        <v>46296</v>
-      </c>
-      <c r="B38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="1">
-        <v>84416666.666666672</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="27">
-        <v>46296</v>
-      </c>
-      <c r="B39" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="1"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="27">
-        <v>46296</v>
-      </c>
-      <c r="B40" t="s">
-        <v>26</v>
-      </c>
-      <c r="C40" s="1"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="27">
-        <v>46296</v>
-      </c>
-      <c r="B41" t="s">
-        <v>27</v>
-      </c>
-      <c r="C41" s="1">
-        <f>C39-C40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="27">
-        <v>46327</v>
-      </c>
-      <c r="B42" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="1">
-        <v>84416666.666666672</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="27">
-        <v>46327</v>
-      </c>
-      <c r="B43" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="1"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="27">
-        <v>46327</v>
-      </c>
-      <c r="B44" t="s">
-        <v>26</v>
-      </c>
-      <c r="C44" s="1"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="27">
-        <v>46327</v>
-      </c>
-      <c r="B45" t="s">
-        <v>27</v>
-      </c>
-      <c r="C45" s="1">
-        <f>C43-C44</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="27">
-        <v>46357</v>
-      </c>
-      <c r="B46" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="1">
-        <v>84416666.666666672</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="27">
-        <v>46357</v>
-      </c>
-      <c r="B47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C47" s="1"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="27">
-        <v>46357</v>
-      </c>
-      <c r="B48" t="s">
-        <v>26</v>
-      </c>
-      <c r="C48" s="1"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="27">
-        <v>46357</v>
-      </c>
-      <c r="B49" t="s">
-        <v>27</v>
-      </c>
-      <c r="C49" s="1">
-        <f>C47-C48</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Gráfico_Grupo de Despesa.xlsx
+++ b/Gráfico_Grupo de Despesa.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Rei-1cpd003\coord_plan_institucional\DADOS CPI\Orçamento\2026\EXECUÇÃO ORÇAMENTÁRIA\RELEXORC_CSV\Saida_PowerBI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C78E0AF-2888-44E8-9688-1C9EF72027F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392F83E7-D7BC-4DC4-94CE-5A14720FE1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BD803231-520B-43E5-B415-970328918330}"/>
   </bookViews>
   <sheets>
-    <sheet name="Receita X Despesa" sheetId="3" r:id="rId1"/>
-    <sheet name="Exec_Por Grupo" sheetId="1" r:id="rId2"/>
-    <sheet name="Planilha1" sheetId="2" r:id="rId3"/>
+    <sheet name="ReceitaXDespesa" sheetId="3" r:id="rId1"/>
+    <sheet name="Exec_Por Grupo" sheetId="1" state="hidden" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Planilha1!$A$1:$P$59</definedName>
